--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:01</t>
+    <t xml:space="preserve">2026-09-24 00:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -681,13 +681,13 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.57</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.63</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="10">
@@ -727,13 +727,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="11">
@@ -750,13 +750,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="12">
@@ -796,13 +796,13 @@
         <v>24</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.22</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="15">
@@ -842,13 +842,13 @@
         <v>24</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.33</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>-0.03</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="16">
@@ -1002,13 +1002,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.6</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.69</v>
       </c>
     </row>
     <row r="24">
@@ -1025,13 +1025,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.61</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="25">
@@ -1048,13 +1048,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="26">
@@ -1071,13 +1071,13 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27">
@@ -1117,13 +1117,13 @@
         <v>24</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.27</v>
+        <v>0.04</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="29">
@@ -1140,13 +1140,13 @@
         <v>24</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.23</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="30">
@@ -1163,13 +1163,13 @@
         <v>24</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.29</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>-0.02</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="31">
@@ -1323,13 +1323,13 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.25</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="39">
@@ -1346,13 +1346,13 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="40">
@@ -1369,13 +1369,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
@@ -1392,13 +1392,13 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="42">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="44">
@@ -1461,13 +1461,13 @@
         <v>24</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="45">
@@ -1484,13 +1484,13 @@
         <v>24</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="46">
@@ -1644,13 +1644,13 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>0.3</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="54">
@@ -1667,13 +1667,13 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="55">
@@ -1696,7 +1696,7 @@
         <v>0.25</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="56">
@@ -1713,13 +1713,13 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="57">
@@ -1759,13 +1759,13 @@
         <v>24</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>-0.14</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="59">
@@ -1782,13 +1782,13 @@
         <v>24</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.26</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="60">
@@ -1968,7 +1968,7 @@
         <v>-0.74</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G68" s="2" t="n">
         <v>-0.71</v>
@@ -1991,7 +1991,7 @@
         <v>-0.37</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>-0.19</v>
@@ -2034,13 +2034,13 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="72">
@@ -2289,10 +2289,10 @@
         <v>-0.49</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="84">
@@ -2312,10 +2312,10 @@
         <v>-0.11</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="85">
@@ -2607,13 +2607,13 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>0.24</v>
+        <v>-0.05</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>-0.24</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.48</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="99">
@@ -2630,13 +2630,13 @@
         <v>18</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.17</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="100">
@@ -2653,13 +2653,13 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="101">
@@ -2676,13 +2676,13 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="102">
@@ -2722,13 +2722,13 @@
         <v>24</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>0.44</v>
+        <v>0.13</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.13</v>
+        <v>0.07</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="104">
@@ -2745,13 +2745,13 @@
         <v>24</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0.59</v>
+        <v>0.18</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.56</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="105">
@@ -2768,13 +2768,13 @@
         <v>24</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="F105" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="106">
@@ -2928,13 +2928,13 @@
         <v>18</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="F113" s="2" t="n">
         <v>-0.36</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="114">
@@ -2951,13 +2951,13 @@
         <v>18</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.41</v>
       </c>
       <c r="F114" s="2" t="n">
         <v>-0.32</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="115">
@@ -2974,13 +2974,13 @@
         <v>18</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="F115" s="2" t="n">
         <v>-0.18</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="116">
@@ -2997,13 +2997,13 @@
         <v>18</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="117">
@@ -3043,13 +3043,13 @@
         <v>24</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0.76</v>
+        <v>0.54</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="119">
@@ -3066,13 +3066,13 @@
         <v>24</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>0.54</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="120">
@@ -3089,13 +3089,13 @@
         <v>24</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="F120" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="121">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_magallanes.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:52</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2019_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
